--- a/cities/development/european_100000pop_comments.xlsx
+++ b/cities/development/european_100000pop_comments.xlsx
@@ -5,25 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianapessoa/Desktop/dataexport/cities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianapessoa/Desktop/dataexport/cities/development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E339698-8143-0C45-AF32-F184CE666376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF10DB0-4617-E849-A683-EE4D60F8E236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3620" yWindow="-28200" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comments" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Comments!$A$1:$H$457</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Comments!$A$1:$L$457</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="650">
   <si>
     <t>name_en</t>
   </si>
@@ -1736,13 +1749,250 @@
   </si>
   <si>
     <t>Polygon is OSM bigger than Maps, but there is not one smaller represented. Includes a nearby national park and another small urbanisation. Could work.</t>
+  </si>
+  <si>
+    <t>Ede 16, Netherlands</t>
+  </si>
+  <si>
+    <t>Emmen 16</t>
+  </si>
+  <si>
+    <t>Frederiksberg Municipality</t>
+  </si>
+  <si>
+    <t>Ivano-Frankivsk, Ivano-Frankivsk</t>
+  </si>
+  <si>
+    <t>León 16, Spain</t>
+  </si>
+  <si>
+    <t>Lida, Belarus</t>
+  </si>
+  <si>
+    <t>Livorno, Livorno</t>
+  </si>
+  <si>
+    <t>Lublin, Lublin Voivodeship</t>
+  </si>
+  <si>
+    <t>Luhansk, Luhansk</t>
+  </si>
+  <si>
+    <t>Montreuil, Ile-de-France</t>
+  </si>
+  <si>
+    <t>Monza, Monza</t>
+  </si>
+  <si>
+    <t>Nis, Serbia</t>
+  </si>
+  <si>
+    <t>Odense Municipality</t>
+  </si>
+  <si>
+    <t>Opole, Opole Voivodeship</t>
+  </si>
+  <si>
+    <t>Padua, Padua</t>
+  </si>
+  <si>
+    <t>Pescara, Pescara</t>
+  </si>
+  <si>
+    <t>Prato, Prato</t>
+  </si>
+  <si>
+    <t>Rivne, Rivne</t>
+  </si>
+  <si>
+    <t>Siegen, Germany</t>
+  </si>
+  <si>
+    <t>Sumy, Sumy</t>
+  </si>
+  <si>
+    <t>Ternopil, Ternopil</t>
+  </si>
+  <si>
+    <t>Thessaloniki Municipal Unit</t>
+  </si>
+  <si>
+    <t>Uzhhorod Urban Hromada</t>
+  </si>
+  <si>
+    <t>Vinnytsia, Vinnytsia</t>
+  </si>
+  <si>
+    <t>Vitebsk, Vitebsk</t>
+  </si>
+  <si>
+    <t>Westland, Netherlands</t>
+  </si>
+  <si>
+    <t>Zhytomyr, Zhytomyr</t>
+  </si>
+  <si>
+    <t>Aalborg Municipality</t>
+  </si>
+  <si>
+    <t>Aarhus Municipality</t>
+  </si>
+  <si>
+    <t>Amersfoort 16</t>
+  </si>
+  <si>
+    <t>Belfast City District</t>
+  </si>
+  <si>
+    <t>Bolzano, Bolzano</t>
+  </si>
+  <si>
+    <t>Brest, Belarus</t>
+  </si>
+  <si>
+    <t>Brescia, Brescia</t>
+  </si>
+  <si>
+    <t>Burgas, Burgas</t>
+  </si>
+  <si>
+    <t>Cardiff, Wales</t>
+  </si>
+  <si>
+    <t>Cherkasy, Cherkasy</t>
+  </si>
+  <si>
+    <t>Chernihiv, Chernihiv</t>
+  </si>
+  <si>
+    <t>Coventry, United Kingdom</t>
+  </si>
+  <si>
+    <t>Donetsk, Donetsk</t>
+  </si>
+  <si>
+    <t>Durrës, Bashkia Durrës, Northern Albania</t>
+  </si>
+  <si>
+    <t>Ferrara, Ferrara</t>
+  </si>
+  <si>
+    <t>Foggia, Foggia</t>
+  </si>
+  <si>
+    <t>Forli, Forli</t>
+  </si>
+  <si>
+    <t>Glasgow City</t>
+  </si>
+  <si>
+    <t>Granada, Spain</t>
+  </si>
+  <si>
+    <t>Heraklion Municipal Unit</t>
+  </si>
+  <si>
+    <t>Kherson, Kherson</t>
+  </si>
+  <si>
+    <t>Municipal Unit of Larissa</t>
+  </si>
+  <si>
+    <t>Latina, Latina</t>
+  </si>
+  <si>
+    <t>Leicester City</t>
+  </si>
+  <si>
+    <t>Modena, Modena</t>
+  </si>
+  <si>
+    <t>Novara, Novara</t>
+  </si>
+  <si>
+    <t>Ourense, Ourense</t>
+  </si>
+  <si>
+    <t>Municipal Unit of Patras</t>
+  </si>
+  <si>
+    <t>Perugia, Perugia</t>
+  </si>
+  <si>
+    <t>Piacenza, Piacenza</t>
+  </si>
+  <si>
+    <t>Plovdiv, Plovdiv</t>
+  </si>
+  <si>
+    <t>Poltava, Poltava</t>
+  </si>
+  <si>
+    <t>Ravenna, Ravenna</t>
+  </si>
+  <si>
+    <t>Reggio Nell'Emilia, Reggio Nell'Emilia</t>
+  </si>
+  <si>
+    <t>Rimini, Rimini</t>
+  </si>
+  <si>
+    <t>Salerno, Salerno</t>
+  </si>
+  <si>
+    <t>Stara Zagora, Stara Zagora</t>
+  </si>
+  <si>
+    <t>Taranto, Taranto</t>
+  </si>
+  <si>
+    <t>Terni, Terni</t>
+  </si>
+  <si>
+    <t>Trento, Trento</t>
+  </si>
+  <si>
+    <t>Vejle Municipality</t>
+  </si>
+  <si>
+    <t>Verona, Verona</t>
+  </si>
+  <si>
+    <t>Vicenza, Vicenza</t>
+  </si>
+  <si>
+    <t>Esbjerg Municipality</t>
+  </si>
+  <si>
+    <t>Bradford, West Yorkshire</t>
+  </si>
+  <si>
+    <t>Nîmes, France</t>
+  </si>
+  <si>
+    <t>Oporto</t>
+  </si>
+  <si>
+    <t>Khmelnytskyi, Khmelnytskyi</t>
+  </si>
+  <si>
+    <t>Lutsk</t>
+  </si>
+  <si>
+    <t>Orebro kommun</t>
+  </si>
+  <si>
+    <t>Parma, Parma</t>
+  </si>
+  <si>
+    <t>Πειραιάς</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1769,6 +2019,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1790,7 +2046,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1800,6 +2056,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2102,7 +2359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H457"/>
+  <dimension ref="A1:L457"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -2197,7 +2454,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>598</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -2223,7 +2480,7 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>599</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -2601,7 +2858,7 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>600</v>
       </c>
       <c r="D20" t="s">
         <v>43</v>
@@ -3017,7 +3274,7 @@
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>601</v>
       </c>
       <c r="D37" t="s">
         <v>72</v>
@@ -3389,7 +3646,7 @@
         <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>602</v>
       </c>
       <c r="D52" t="s">
         <v>89</v>
@@ -3563,7 +3820,7 @@
         <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>642</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -3711,7 +3968,7 @@
         <v>66</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>604</v>
       </c>
       <c r="D65" t="s">
         <v>102</v>
@@ -3737,7 +3994,7 @@
         <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>603</v>
       </c>
       <c r="D66" t="s">
         <v>103</v>
@@ -3909,7 +4166,7 @@
         <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>605</v>
       </c>
       <c r="D73" t="s">
         <v>112</v>
@@ -4085,7 +4342,7 @@
         <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>606</v>
       </c>
       <c r="D80" t="s">
         <v>123</v>
@@ -4235,7 +4492,7 @@
         <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>607</v>
       </c>
       <c r="D86" t="s">
         <v>129</v>
@@ -4259,7 +4516,7 @@
         <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>608</v>
       </c>
       <c r="D87" t="s">
         <v>130</v>
@@ -4479,7 +4736,7 @@
         <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>142</v>
+        <v>609</v>
       </c>
       <c r="D96" t="s">
         <v>142</v>
@@ -4695,7 +4952,7 @@
         <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>610</v>
       </c>
       <c r="D105" t="s">
         <v>156</v>
@@ -4869,7 +5126,7 @@
         <v>164</v>
       </c>
       <c r="C112" t="s">
-        <v>163</v>
+        <v>611</v>
       </c>
       <c r="D112" t="s">
         <v>163</v>
@@ -4917,7 +5174,7 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>167</v>
+        <v>571</v>
       </c>
       <c r="D114" t="s">
         <v>167</v>
@@ -5043,7 +5300,7 @@
         <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>172</v>
+        <v>572</v>
       </c>
       <c r="D119" t="s">
         <v>172</v>
@@ -5141,7 +5398,7 @@
         <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>176</v>
+        <v>641</v>
       </c>
       <c r="D123" t="s">
         <v>176</v>
@@ -5215,7 +5472,7 @@
         <v>66</v>
       </c>
       <c r="C126" t="s">
-        <v>181</v>
+        <v>612</v>
       </c>
       <c r="D126" t="s">
         <v>181</v>
@@ -5267,7 +5524,7 @@
         <v>66</v>
       </c>
       <c r="C128" t="s">
-        <v>184</v>
+        <v>613</v>
       </c>
       <c r="D128" t="s">
         <v>184</v>
@@ -5293,7 +5550,7 @@
         <v>66</v>
       </c>
       <c r="C129" t="s">
-        <v>185</v>
+        <v>614</v>
       </c>
       <c r="D129" t="s">
         <v>185</v>
@@ -5343,7 +5600,7 @@
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>187</v>
+        <v>573</v>
       </c>
       <c r="D131" t="s">
         <v>187</v>
@@ -5715,7 +5972,7 @@
         <v>20</v>
       </c>
       <c r="C146" t="s">
-        <v>205</v>
+        <v>615</v>
       </c>
       <c r="D146" t="s">
         <v>205</v>
@@ -5813,7 +6070,7 @@
         <v>210</v>
       </c>
       <c r="C150" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D150" t="s">
         <v>211</v>
@@ -5861,7 +6118,7 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>213</v>
+        <v>616</v>
       </c>
       <c r="D152" t="s">
         <v>213</v>
@@ -6277,7 +6534,7 @@
         <v>121</v>
       </c>
       <c r="C169" t="s">
-        <v>234</v>
+        <v>617</v>
       </c>
       <c r="D169" t="s">
         <v>235</v>
@@ -6451,7 +6708,7 @@
         <v>28</v>
       </c>
       <c r="C176" t="s">
-        <v>243</v>
+        <v>574</v>
       </c>
       <c r="D176" t="s">
         <v>243</v>
@@ -6821,7 +7078,7 @@
         <v>28</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>618</v>
       </c>
       <c r="D191" t="s">
         <v>259</v>
@@ -6847,7 +7104,7 @@
         <v>28</v>
       </c>
       <c r="C192" t="s">
-        <v>260</v>
+        <v>645</v>
       </c>
       <c r="D192" t="s">
         <v>260</v>
@@ -7307,7 +7564,7 @@
         <v>121</v>
       </c>
       <c r="C211" t="s">
-        <v>286</v>
+        <v>619</v>
       </c>
       <c r="D211" t="s">
         <v>286</v>
@@ -7359,7 +7616,7 @@
         <v>66</v>
       </c>
       <c r="C213" t="s">
-        <v>288</v>
+        <v>620</v>
       </c>
       <c r="D213" t="s">
         <v>288</v>
@@ -7535,7 +7792,7 @@
         <v>20</v>
       </c>
       <c r="C220" t="s">
-        <v>295</v>
+        <v>621</v>
       </c>
       <c r="D220" t="s">
         <v>295</v>
@@ -7607,7 +7864,7 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>299</v>
+        <v>575</v>
       </c>
       <c r="D223" t="s">
         <v>299</v>
@@ -7681,7 +7938,7 @@
         <v>62</v>
       </c>
       <c r="C226" t="s">
-        <v>301</v>
+        <v>576</v>
       </c>
       <c r="D226" t="s">
         <v>301</v>
@@ -7853,7 +8110,7 @@
         <v>66</v>
       </c>
       <c r="C233" t="s">
-        <v>307</v>
+        <v>577</v>
       </c>
       <c r="D233" t="s">
         <v>307</v>
@@ -7979,7 +8236,7 @@
         <v>78</v>
       </c>
       <c r="C238" t="s">
-        <v>313</v>
+        <v>578</v>
       </c>
       <c r="D238" t="s">
         <v>313</v>
@@ -8027,7 +8284,7 @@
         <v>28</v>
       </c>
       <c r="C240" t="s">
-        <v>315</v>
+        <v>579</v>
       </c>
       <c r="D240" t="s">
         <v>316</v>
@@ -8077,7 +8334,7 @@
         <v>28</v>
       </c>
       <c r="C242" t="s">
-        <v>318</v>
+        <v>646</v>
       </c>
       <c r="D242" t="s">
         <v>318</v>
@@ -8577,7 +8834,7 @@
         <v>66</v>
       </c>
       <c r="C262" t="s">
-        <v>340</v>
+        <v>622</v>
       </c>
       <c r="D262" t="s">
         <v>340</v>
@@ -8699,7 +8956,7 @@
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>344</v>
+        <v>580</v>
       </c>
       <c r="D267" t="s">
         <v>344</v>
@@ -8723,7 +8980,7 @@
         <v>66</v>
       </c>
       <c r="C268" t="s">
-        <v>345</v>
+        <v>581</v>
       </c>
       <c r="D268" t="s">
         <v>345</v>
@@ -8841,7 +9098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>348</v>
       </c>
@@ -8864,8 +9121,9 @@
       <c r="H273">
         <v>1</v>
       </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="L273" s="5"/>
+    </row>
+    <row r="274" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>357</v>
       </c>
@@ -8888,8 +9146,9 @@
       <c r="H274">
         <v>1</v>
       </c>
-    </row>
-    <row r="275" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="L274" s="5"/>
+    </row>
+    <row r="275" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>350</v>
       </c>
@@ -8914,8 +9173,9 @@
       <c r="H275">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="L275" s="5"/>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>351</v>
       </c>
@@ -8939,7 +9199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>358</v>
       </c>
@@ -8963,7 +9223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>359</v>
       </c>
@@ -8987,7 +9247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>360</v>
       </c>
@@ -9011,7 +9271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>361</v>
       </c>
@@ -9037,7 +9297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>363</v>
       </c>
@@ -9061,7 +9321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>364</v>
       </c>
@@ -9085,7 +9345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>365</v>
       </c>
@@ -9109,7 +9369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>366</v>
       </c>
@@ -9135,7 +9395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>367</v>
       </c>
@@ -9161,7 +9421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>378</v>
       </c>
@@ -9169,7 +9429,7 @@
         <v>23</v>
       </c>
       <c r="C286" t="s">
-        <v>378</v>
+        <v>643</v>
       </c>
       <c r="D286" t="s">
         <v>378</v>
@@ -9185,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>368</v>
       </c>
@@ -9193,7 +9453,7 @@
         <v>272</v>
       </c>
       <c r="C287" t="s">
-        <v>368</v>
+        <v>582</v>
       </c>
       <c r="D287" t="s">
         <v>369</v>
@@ -9209,7 +9469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>370</v>
       </c>
@@ -9293,7 +9553,7 @@
         <v>66</v>
       </c>
       <c r="C291" t="s">
-        <v>373</v>
+        <v>623</v>
       </c>
       <c r="D291" t="s">
         <v>373</v>
@@ -9415,7 +9675,7 @@
         <v>14</v>
       </c>
       <c r="C296" t="s">
-        <v>380</v>
+        <v>583</v>
       </c>
       <c r="D296" t="s">
         <v>380</v>
@@ -9561,7 +9821,7 @@
         <v>78</v>
       </c>
       <c r="C302" t="s">
-        <v>386</v>
+        <v>584</v>
       </c>
       <c r="D302" t="s">
         <v>386</v>
@@ -9585,7 +9845,7 @@
         <v>210</v>
       </c>
       <c r="C303" t="s">
-        <v>387</v>
+        <v>647</v>
       </c>
       <c r="D303" t="s">
         <v>387</v>
@@ -9757,7 +10017,7 @@
         <v>8</v>
       </c>
       <c r="C310" t="s">
-        <v>396</v>
+        <v>624</v>
       </c>
       <c r="D310" t="s">
         <v>396</v>
@@ -9833,7 +10093,7 @@
         <v>66</v>
       </c>
       <c r="C313" t="s">
-        <v>399</v>
+        <v>585</v>
       </c>
       <c r="D313" t="s">
         <v>400</v>
@@ -9961,7 +10221,7 @@
         <v>66</v>
       </c>
       <c r="C318" t="s">
-        <v>405</v>
+        <v>648</v>
       </c>
       <c r="D318" t="s">
         <v>405</v>
@@ -9987,7 +10247,7 @@
         <v>121</v>
       </c>
       <c r="C319" t="s">
-        <v>406</v>
+        <v>625</v>
       </c>
       <c r="D319" t="s">
         <v>407</v>
@@ -10111,7 +10371,7 @@
         <v>66</v>
       </c>
       <c r="C324" t="s">
-        <v>410</v>
+        <v>626</v>
       </c>
       <c r="D324" t="s">
         <v>410</v>
@@ -10137,7 +10397,7 @@
         <v>66</v>
       </c>
       <c r="C325" t="s">
-        <v>411</v>
+        <v>586</v>
       </c>
       <c r="D325" t="s">
         <v>411</v>
@@ -10187,7 +10447,7 @@
         <v>66</v>
       </c>
       <c r="C327" t="s">
-        <v>413</v>
+        <v>627</v>
       </c>
       <c r="D327" t="s">
         <v>413</v>
@@ -10261,7 +10521,7 @@
         <v>121</v>
       </c>
       <c r="C330" t="s">
-        <v>417</v>
+        <v>649</v>
       </c>
       <c r="D330" t="s">
         <v>418</v>
@@ -10309,7 +10569,7 @@
         <v>113</v>
       </c>
       <c r="C332" t="s">
-        <v>420</v>
+        <v>628</v>
       </c>
       <c r="D332" t="s">
         <v>420</v>
@@ -10357,7 +10617,7 @@
         <v>28</v>
       </c>
       <c r="C334" t="s">
-        <v>422</v>
+        <v>629</v>
       </c>
       <c r="D334" t="s">
         <v>422</v>
@@ -10381,7 +10641,7 @@
         <v>41</v>
       </c>
       <c r="C335" t="s">
-        <v>423</v>
+        <v>644</v>
       </c>
       <c r="D335" t="s">
         <v>423</v>
@@ -10477,7 +10737,7 @@
         <v>66</v>
       </c>
       <c r="C339" t="s">
-        <v>427</v>
+        <v>587</v>
       </c>
       <c r="D339" t="s">
         <v>427</v>
@@ -10529,7 +10789,7 @@
         <v>66</v>
       </c>
       <c r="C341" t="s">
-        <v>431</v>
+        <v>630</v>
       </c>
       <c r="D341" t="s">
         <v>431</v>
@@ -10655,7 +10915,7 @@
         <v>66</v>
       </c>
       <c r="C346" t="s">
-        <v>436</v>
+        <v>631</v>
       </c>
       <c r="D346" t="s">
         <v>436</v>
@@ -10827,7 +11087,7 @@
         <v>66</v>
       </c>
       <c r="C353" t="s">
-        <v>443</v>
+        <v>632</v>
       </c>
       <c r="D353" t="s">
         <v>443</v>
@@ -10853,7 +11113,7 @@
         <v>28</v>
       </c>
       <c r="C354" t="s">
-        <v>444</v>
+        <v>588</v>
       </c>
       <c r="D354" t="s">
         <v>444</v>
@@ -11197,7 +11457,7 @@
         <v>66</v>
       </c>
       <c r="C368" t="s">
-        <v>457</v>
+        <v>633</v>
       </c>
       <c r="D368" t="s">
         <v>457</v>
@@ -11499,7 +11759,7 @@
         <v>11</v>
       </c>
       <c r="C380" t="s">
-        <v>470</v>
+        <v>589</v>
       </c>
       <c r="D380" t="s">
         <v>470</v>
@@ -11671,7 +11931,7 @@
         <v>113</v>
       </c>
       <c r="C387" t="s">
-        <v>477</v>
+        <v>634</v>
       </c>
       <c r="D387" t="s">
         <v>477</v>
@@ -11795,7 +12055,7 @@
         <v>28</v>
       </c>
       <c r="C392" t="s">
-        <v>482</v>
+        <v>590</v>
       </c>
       <c r="D392" t="s">
         <v>482</v>
@@ -11919,7 +12179,7 @@
         <v>66</v>
       </c>
       <c r="C397" t="s">
-        <v>488</v>
+        <v>635</v>
       </c>
       <c r="D397" t="s">
         <v>488</v>
@@ -12021,7 +12281,7 @@
         <v>66</v>
       </c>
       <c r="C401" t="s">
-        <v>492</v>
+        <v>636</v>
       </c>
       <c r="D401" t="s">
         <v>492</v>
@@ -12047,7 +12307,7 @@
         <v>28</v>
       </c>
       <c r="C402" t="s">
-        <v>493</v>
+        <v>591</v>
       </c>
       <c r="D402" t="s">
         <v>493</v>
@@ -12123,7 +12383,7 @@
         <v>121</v>
       </c>
       <c r="C405" t="s">
-        <v>497</v>
+        <v>592</v>
       </c>
       <c r="D405" t="s">
         <v>497</v>
@@ -12295,7 +12555,7 @@
         <v>66</v>
       </c>
       <c r="C412" t="s">
-        <v>504</v>
+        <v>637</v>
       </c>
       <c r="D412" t="s">
         <v>504</v>
@@ -12543,7 +12803,7 @@
         <v>28</v>
       </c>
       <c r="C422" t="s">
-        <v>515</v>
+        <v>593</v>
       </c>
       <c r="D422" t="s">
         <v>515</v>
@@ -12695,7 +12955,7 @@
         <v>14</v>
       </c>
       <c r="C428" t="s">
-        <v>521</v>
+        <v>638</v>
       </c>
       <c r="D428" t="s">
         <v>521</v>
@@ -12771,7 +13031,7 @@
         <v>66</v>
       </c>
       <c r="C431" t="s">
-        <v>525</v>
+        <v>639</v>
       </c>
       <c r="D431" t="s">
         <v>525</v>
@@ -12797,7 +13057,7 @@
         <v>66</v>
       </c>
       <c r="C432" t="s">
-        <v>526</v>
+        <v>640</v>
       </c>
       <c r="D432" t="s">
         <v>526</v>
@@ -12899,7 +13159,7 @@
         <v>28</v>
       </c>
       <c r="C436" t="s">
-        <v>530</v>
+        <v>594</v>
       </c>
       <c r="D436" t="s">
         <v>531</v>
@@ -12925,7 +13185,7 @@
         <v>62</v>
       </c>
       <c r="C437" t="s">
-        <v>532</v>
+        <v>595</v>
       </c>
       <c r="D437" t="s">
         <v>532</v>
@@ -12999,7 +13259,7 @@
         <v>35</v>
       </c>
       <c r="C440" t="s">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="D440" t="s">
         <v>536</v>
@@ -13317,7 +13577,7 @@
         <v>28</v>
       </c>
       <c r="C453" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="D453" t="s">
         <v>550</v>

--- a/cities/development/european_100000pop_comments.xlsx
+++ b/cities/development/european_100000pop_comments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianapessoa/Desktop/dataexport/cities/development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF10DB0-4617-E849-A683-EE4D60F8E236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D2CFBB-A902-374B-AF4F-62C186A0699D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2469,7 +2469,7 @@
         <v>557</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2495,7 +2495,7 @@
         <v>557</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -5413,7 +5413,7 @@
         <v>557</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -12970,7 +12970,7 @@
         <v>557</v>
       </c>
       <c r="H428">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
